--- a/thaco/color/1_DATA_NoAllowance.xlsx
+++ b/thaco/color/1_DATA_NoAllowance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32701B3C-3C0B-3B4B-8A3C-2A6F4DC645A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68CD6084-80F5-EA43-A4C9-57645BAB991C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2140" yWindow="720" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4440" yWindow="680" windowWidth="33760" windowHeight="18480" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="5" r:id="rId1"/>
@@ -4160,203 +4160,10 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={3B7FFEF4-AE63-4DFA-B536-7BAA2BEE4A14}</author>
-    <author>tc={F2CA1CEE-0407-4ECA-B543-A94DFE1E09BB}</author>
-  </authors>
-  <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{7F1822B3-CF41-9C4C-AF6A-101E0D0CD369}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    TV: Thử việc
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t>CT: Chính thức</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{894EFCB7-ADAC-6A40-AF91-4567D0ABDEB0}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Threaded comment]
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Comment:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    Đối tượng Lương ngày tại các TĐTV
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Reply:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">    LT: Lương Tháng
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">LN: Lương ngày
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>MSNV</t>
-  </si>
-  <si>
-    <t>Full name</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Type of labor contract</t>
-  </si>
-  <si>
-    <t>Subjects are counted as working overtime</t>
-  </si>
-  <si>
-    <t>Is a dispatcher, fire protection officer, and AT-VSV</t>
   </si>
   <si>
     <t>Cong goes to work on weekdays</t>
@@ -4407,67 +4214,13 @@
     <t>From the 15th onwards</t>
   </si>
   <si>
-    <t>CT</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
     <t>2504023</t>
   </si>
   <si>
     <t>2305991</t>
   </si>
   <si>
-    <t>LN</t>
-  </si>
-  <si>
-    <t>TV</t>
-  </si>
-  <si>
     <t>2006324</t>
-  </si>
-  <si>
-    <t>AT-VSV</t>
-  </si>
-  <si>
-    <t>Tô Thanh Liêm</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành An</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Thọ</t>
-  </si>
-  <si>
-    <t>Trương Thị Thu Hiền</t>
-  </si>
-  <si>
-    <t>Võ Thị Tú Trinh</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thủy Tiên</t>
-  </si>
-  <si>
-    <t>ĐP PCCC</t>
-  </si>
-  <si>
-    <t>Nguyễn Hồng Nhung</t>
-  </si>
-  <si>
-    <t>Accounting department</t>
-  </si>
-  <si>
-    <t>Human Resources Department</t>
-  </si>
-  <si>
-    <t>Finance Department</t>
-  </si>
-  <si>
-    <t>Administrative Department</t>
-  </si>
-  <si>
-    <t>Digital Transformation Department</t>
   </si>
   <si>
     <t>Realization part 1</t>
@@ -4483,7 +4236,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4561,12 +4314,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -4582,17 +4329,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <sz val="13"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4602,7 +4338,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -4665,21 +4401,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -4698,7 +4419,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4739,14 +4460,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4758,22 +4478,10 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4797,35 +4505,18 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4834,10 +4525,7 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5222,827 +4910,662 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D8D00B-A9B3-3D49-B6EF-A5F131B8B277}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D8D00B-A9B3-3D49-B6EF-A5F131B8B277}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:AB18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A1:W18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="8.5" style="37" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" style="45" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" style="39" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="14" style="39" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="11.5" style="40" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="19" width="7.1640625" style="42" customWidth="1"/>
-    <col min="20" max="21" width="10.5" style="41" customWidth="1"/>
-    <col min="22" max="22" width="12.5" style="41" customWidth="1"/>
-    <col min="23" max="23" width="10.6640625" style="43" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="19.5" style="44" customWidth="1"/>
-    <col min="25" max="25" width="12.33203125" style="44" customWidth="1"/>
-    <col min="26" max="26" width="12.5" style="44" customWidth="1"/>
-    <col min="27" max="27" width="11.6640625" style="44" customWidth="1"/>
-    <col min="28" max="16384" width="9.1640625" style="44"/>
+    <col min="1" max="1" width="8.5" style="32" customWidth="1"/>
+    <col min="2" max="15" width="7.1640625" style="34" customWidth="1"/>
+    <col min="16" max="17" width="10.5" style="33" customWidth="1"/>
+    <col min="18" max="18" width="12.5" style="33" customWidth="1"/>
+    <col min="19" max="19" width="19.5" style="35" customWidth="1"/>
+    <col min="20" max="20" width="12.33203125" style="35" customWidth="1"/>
+    <col min="21" max="21" width="12.5" style="35" customWidth="1"/>
+    <col min="22" max="22" width="11.6640625" style="35" customWidth="1"/>
+    <col min="23" max="16384" width="9.1640625" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="54" customFormat="1" ht="54" customHeight="1" outlineLevel="1">
-      <c r="A1" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="47" t="s">
+    <row r="1" spans="1:23" s="41" customFormat="1" ht="54" customHeight="1" outlineLevel="1">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="48" t="s">
+      <c r="C1" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="48" t="s">
+      <c r="D1" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="49" t="s">
+      <c r="H1" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="I1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="J1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="49" t="s">
+      <c r="K1" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="49" t="s">
+      <c r="L1" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="49" t="s">
+      <c r="M1" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="49" t="s">
+      <c r="P1" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="49" t="s">
+      <c r="Q1" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="49" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q1" s="50" t="s">
+      <c r="R1" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="R1" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="S1" s="49" t="s">
+    </row>
+    <row r="2" spans="1:23" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
+      <c r="A2" s="23">
+        <v>2405236</v>
+      </c>
+      <c r="B2" s="24">
+        <v>26</v>
+      </c>
+      <c r="C2" s="24">
+        <v>0</v>
+      </c>
+      <c r="D2" s="24">
+        <v>0</v>
+      </c>
+      <c r="E2" s="24">
+        <v>0</v>
+      </c>
+      <c r="F2" s="24">
+        <v>0</v>
+      </c>
+      <c r="G2" s="24">
+        <v>0</v>
+      </c>
+      <c r="H2" s="24">
+        <v>0</v>
+      </c>
+      <c r="I2" s="24">
+        <v>0</v>
+      </c>
+      <c r="J2" s="24">
+        <v>0</v>
+      </c>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24">
+        <v>0</v>
+      </c>
+      <c r="M2" s="24">
+        <v>0</v>
+      </c>
+      <c r="N2" s="24">
+        <v>0</v>
+      </c>
+      <c r="O2" s="24">
+        <v>0</v>
+      </c>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="33"/>
+    </row>
+    <row r="3" spans="1:23" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
+      <c r="A3" s="23">
+        <v>2106723</v>
+      </c>
+      <c r="B3" s="24">
+        <v>19</v>
+      </c>
+      <c r="C3" s="24">
+        <v>5</v>
+      </c>
+      <c r="D3" s="24">
+        <v>0</v>
+      </c>
+      <c r="E3" s="24">
+        <v>0</v>
+      </c>
+      <c r="F3" s="24">
+        <v>0</v>
+      </c>
+      <c r="G3" s="24">
+        <v>0</v>
+      </c>
+      <c r="H3" s="24">
+        <v>0</v>
+      </c>
+      <c r="I3" s="24">
+        <v>0</v>
+      </c>
+      <c r="J3" s="24">
+        <v>0</v>
+      </c>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24">
+        <v>0</v>
+      </c>
+      <c r="M3" s="24">
+        <v>0</v>
+      </c>
+      <c r="N3" s="24">
+        <v>0</v>
+      </c>
+      <c r="O3" s="24">
+        <v>0</v>
+      </c>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="33"/>
+    </row>
+    <row r="4" spans="1:23" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
+      <c r="A4" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="51" t="s">
+      <c r="B4" s="24">
+        <v>24</v>
+      </c>
+      <c r="C4" s="24">
+        <v>0</v>
+      </c>
+      <c r="D4" s="24">
+        <v>0</v>
+      </c>
+      <c r="E4" s="24">
+        <v>0</v>
+      </c>
+      <c r="F4" s="24">
+        <v>0</v>
+      </c>
+      <c r="G4" s="24">
+        <v>0</v>
+      </c>
+      <c r="H4" s="24">
+        <v>0</v>
+      </c>
+      <c r="I4" s="24">
+        <v>0</v>
+      </c>
+      <c r="J4" s="24">
+        <v>0</v>
+      </c>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24">
+        <v>2</v>
+      </c>
+      <c r="M4" s="24">
+        <v>0</v>
+      </c>
+      <c r="N4" s="24">
+        <v>0</v>
+      </c>
+      <c r="O4" s="24">
+        <v>0</v>
+      </c>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="33"/>
+    </row>
+    <row r="5" spans="1:23" s="18" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A5" s="23">
+        <v>2406198</v>
+      </c>
+      <c r="B5" s="24">
+        <v>23</v>
+      </c>
+      <c r="C5" s="24">
+        <v>3</v>
+      </c>
+      <c r="D5" s="24">
+        <v>0</v>
+      </c>
+      <c r="E5" s="24">
+        <v>0</v>
+      </c>
+      <c r="F5" s="24">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24">
+        <v>0</v>
+      </c>
+      <c r="H5" s="24">
+        <v>0</v>
+      </c>
+      <c r="I5" s="24">
+        <v>0</v>
+      </c>
+      <c r="J5" s="24">
+        <v>0</v>
+      </c>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24">
+        <v>0</v>
+      </c>
+      <c r="M5" s="24">
+        <v>0</v>
+      </c>
+      <c r="N5" s="24">
+        <v>0</v>
+      </c>
+      <c r="O5" s="24">
+        <v>0</v>
+      </c>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="33"/>
+      <c r="V5" s="19"/>
+      <c r="W5" s="20"/>
+    </row>
+    <row r="6" spans="1:23" s="18" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A6" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="51" t="s">
+      <c r="B6" s="24">
+        <v>22</v>
+      </c>
+      <c r="C6" s="24">
+        <v>0</v>
+      </c>
+      <c r="D6" s="24">
+        <v>2</v>
+      </c>
+      <c r="E6" s="24">
+        <v>2</v>
+      </c>
+      <c r="F6" s="24">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24">
+        <v>0</v>
+      </c>
+      <c r="H6" s="24">
+        <v>0</v>
+      </c>
+      <c r="I6" s="24">
+        <v>0</v>
+      </c>
+      <c r="J6" s="24">
+        <v>2</v>
+      </c>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24">
+        <v>0</v>
+      </c>
+      <c r="M6" s="24">
+        <v>0</v>
+      </c>
+      <c r="N6" s="24">
+        <v>0</v>
+      </c>
+      <c r="O6" s="24">
+        <v>0</v>
+      </c>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="25"/>
+      <c r="R6" s="33"/>
+      <c r="V6" s="19"/>
+      <c r="W6" s="20"/>
+    </row>
+    <row r="7" spans="1:23" s="21" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A7" s="23">
+        <v>2406145</v>
+      </c>
+      <c r="B7" s="24">
+        <v>26</v>
+      </c>
+      <c r="C7" s="24">
+        <v>0</v>
+      </c>
+      <c r="D7" s="24">
+        <v>0</v>
+      </c>
+      <c r="E7" s="24">
+        <v>0</v>
+      </c>
+      <c r="F7" s="24">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24">
+        <v>0</v>
+      </c>
+      <c r="H7" s="24">
+        <v>0</v>
+      </c>
+      <c r="I7" s="24">
+        <v>0</v>
+      </c>
+      <c r="J7" s="24">
+        <v>0</v>
+      </c>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24">
+        <v>0</v>
+      </c>
+      <c r="M7" s="24">
+        <v>0</v>
+      </c>
+      <c r="N7" s="24">
+        <v>0</v>
+      </c>
+      <c r="O7" s="24">
+        <v>0</v>
+      </c>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="33"/>
+      <c r="V7" s="19"/>
+      <c r="W7" s="20"/>
+    </row>
+    <row r="8" spans="1:23" s="21" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A8" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="52" t="s">
-        <v>43</v>
-      </c>
-      <c r="W1" s="53" t="s">
+      <c r="B8" s="24">
+        <v>26</v>
+      </c>
+      <c r="C8" s="24">
+        <v>0</v>
+      </c>
+      <c r="D8" s="24">
+        <v>0</v>
+      </c>
+      <c r="E8" s="24">
+        <v>0</v>
+      </c>
+      <c r="F8" s="24">
+        <v>0</v>
+      </c>
+      <c r="G8" s="24">
         <v>5</v>
       </c>
+      <c r="H8" s="24">
+        <v>2</v>
+      </c>
+      <c r="I8" s="24">
+        <v>0</v>
+      </c>
+      <c r="J8" s="24">
+        <v>0</v>
+      </c>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24">
+        <v>0</v>
+      </c>
+      <c r="M8" s="24">
+        <v>0</v>
+      </c>
+      <c r="N8" s="24">
+        <v>0</v>
+      </c>
+      <c r="O8" s="24">
+        <v>0</v>
+      </c>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="22"/>
+      <c r="V8" s="19"/>
+      <c r="W8" s="20"/>
     </row>
-    <row r="2" spans="1:28" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A2" s="24">
-        <v>2405236</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="28">
-        <v>26</v>
-      </c>
-      <c r="G2" s="28">
-        <v>0</v>
-      </c>
-      <c r="H2" s="28">
-        <v>0</v>
-      </c>
-      <c r="I2" s="28">
-        <v>0</v>
-      </c>
-      <c r="J2" s="28">
-        <v>0</v>
-      </c>
-      <c r="K2" s="28">
-        <v>0</v>
-      </c>
-      <c r="L2" s="28">
-        <v>0</v>
-      </c>
-      <c r="M2" s="28">
-        <v>0</v>
-      </c>
-      <c r="N2" s="28">
-        <v>0</v>
-      </c>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="28">
-        <v>0</v>
-      </c>
-      <c r="R2" s="28">
-        <v>0</v>
-      </c>
-      <c r="S2" s="28">
-        <v>0</v>
-      </c>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="30"/>
-    </row>
-    <row r="3" spans="1:28" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A3" s="24">
-        <v>2106723</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="28">
-        <v>19</v>
-      </c>
-      <c r="G3" s="28">
-        <v>5</v>
-      </c>
-      <c r="H3" s="28">
-        <v>0</v>
-      </c>
-      <c r="I3" s="28">
-        <v>0</v>
-      </c>
-      <c r="J3" s="28">
-        <v>0</v>
-      </c>
-      <c r="K3" s="28">
-        <v>0</v>
-      </c>
-      <c r="L3" s="28">
-        <v>0</v>
-      </c>
-      <c r="M3" s="28">
-        <v>0</v>
-      </c>
-      <c r="N3" s="28">
-        <v>0</v>
-      </c>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="28">
-        <v>0</v>
-      </c>
-      <c r="R3" s="28">
-        <v>0</v>
-      </c>
-      <c r="S3" s="28">
-        <v>0</v>
-      </c>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="30"/>
-    </row>
-    <row r="4" spans="1:28" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A4" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="28">
-        <v>24</v>
-      </c>
-      <c r="G4" s="28">
-        <v>0</v>
-      </c>
-      <c r="H4" s="28">
-        <v>0</v>
-      </c>
-      <c r="I4" s="28">
-        <v>0</v>
-      </c>
-      <c r="J4" s="28">
-        <v>0</v>
-      </c>
-      <c r="K4" s="28">
-        <v>0</v>
-      </c>
-      <c r="L4" s="28">
-        <v>0</v>
-      </c>
-      <c r="M4" s="28">
-        <v>0</v>
-      </c>
-      <c r="N4" s="28">
-        <v>0</v>
-      </c>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="28">
-        <v>0</v>
-      </c>
-      <c r="R4" s="28">
-        <v>0</v>
-      </c>
-      <c r="S4" s="28">
-        <v>0</v>
-      </c>
-      <c r="T4" s="29"/>
-      <c r="U4" s="29"/>
-      <c r="V4" s="41"/>
-      <c r="W4" s="30"/>
-    </row>
-    <row r="5" spans="1:28" s="19" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A5" s="24">
-        <v>2406198</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="28">
-        <v>23</v>
-      </c>
-      <c r="G5" s="28">
-        <v>3</v>
-      </c>
-      <c r="H5" s="28">
-        <v>0</v>
-      </c>
-      <c r="I5" s="28">
-        <v>0</v>
-      </c>
-      <c r="J5" s="28">
-        <v>0</v>
-      </c>
-      <c r="K5" s="28">
-        <v>0</v>
-      </c>
-      <c r="L5" s="28">
-        <v>0</v>
-      </c>
-      <c r="M5" s="28">
-        <v>0</v>
-      </c>
-      <c r="N5" s="28">
-        <v>0</v>
-      </c>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="28">
-        <v>0</v>
-      </c>
-      <c r="R5" s="28">
-        <v>0</v>
-      </c>
-      <c r="S5" s="28">
-        <v>0</v>
-      </c>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="30"/>
-      <c r="AA5" s="20"/>
-      <c r="AB5" s="21"/>
-    </row>
-    <row r="6" spans="1:28" s="19" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A6" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="28">
-        <v>22</v>
-      </c>
-      <c r="G6" s="28">
-        <v>0</v>
-      </c>
-      <c r="H6" s="28">
-        <v>2</v>
-      </c>
-      <c r="I6" s="28">
-        <v>2</v>
-      </c>
-      <c r="J6" s="28">
-        <v>0</v>
-      </c>
-      <c r="K6" s="28">
-        <v>0</v>
-      </c>
-      <c r="L6" s="28">
-        <v>0</v>
-      </c>
-      <c r="M6" s="28">
-        <v>0</v>
-      </c>
-      <c r="N6" s="28">
-        <v>2</v>
-      </c>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="28">
-        <v>0</v>
-      </c>
-      <c r="R6" s="28">
-        <v>0</v>
-      </c>
-      <c r="S6" s="28">
-        <v>0</v>
-      </c>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="30"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="21"/>
-    </row>
-    <row r="7" spans="1:28" s="22" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A7" s="24">
-        <v>2406145</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="28">
-        <v>26</v>
-      </c>
-      <c r="G7" s="28">
-        <v>0</v>
-      </c>
-      <c r="H7" s="28">
-        <v>0</v>
-      </c>
-      <c r="I7" s="28">
-        <v>0</v>
-      </c>
-      <c r="J7" s="28">
-        <v>0</v>
-      </c>
-      <c r="K7" s="28">
-        <v>0</v>
-      </c>
-      <c r="L7" s="28">
-        <v>0</v>
-      </c>
-      <c r="M7" s="28">
-        <v>0</v>
-      </c>
-      <c r="N7" s="28">
-        <v>0</v>
-      </c>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="28">
-        <v>0</v>
-      </c>
-      <c r="R7" s="28">
-        <v>0</v>
-      </c>
-      <c r="S7" s="28">
-        <v>0</v>
-      </c>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="41"/>
-      <c r="W7" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA7" s="20"/>
-      <c r="AB7" s="21"/>
-    </row>
-    <row r="8" spans="1:28" s="22" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A8" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="28">
-        <v>26</v>
-      </c>
-      <c r="G8" s="28">
-        <v>0</v>
-      </c>
-      <c r="H8" s="28">
-        <v>0</v>
-      </c>
-      <c r="I8" s="28">
-        <v>0</v>
-      </c>
-      <c r="J8" s="28">
-        <v>0</v>
-      </c>
-      <c r="K8" s="28">
-        <v>5</v>
-      </c>
-      <c r="L8" s="28">
-        <v>2</v>
-      </c>
-      <c r="M8" s="28">
-        <v>0</v>
-      </c>
-      <c r="N8" s="28">
-        <v>0</v>
-      </c>
-      <c r="O8" s="28"/>
-      <c r="P8" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="28">
-        <v>0</v>
-      </c>
-      <c r="R8" s="28">
-        <v>0</v>
-      </c>
-      <c r="S8" s="28">
-        <v>0</v>
-      </c>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="41"/>
-      <c r="W8" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="23"/>
-      <c r="AA8" s="20"/>
-      <c r="AB8" s="21"/>
-    </row>
-    <row r="9" spans="1:28" s="35" customFormat="1" ht="18">
+    <row r="9" spans="1:23" s="30" customFormat="1" ht="18">
       <c r="A9" s="3"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="18"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="32"/>
-      <c r="AA9" s="33"/>
-      <c r="AB9" s="34"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="29"/>
     </row>
-    <row r="10" spans="1:28" s="35" customFormat="1" ht="20">
+    <row r="10" spans="1:23" s="30" customFormat="1" ht="20">
       <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="14"/>
-      <c r="Q10" s="12"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
       <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="32"/>
-      <c r="AA10" s="33"/>
-      <c r="AB10" s="34"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="29"/>
     </row>
-    <row r="11" spans="1:28" s="35" customFormat="1" ht="20">
+    <row r="11" spans="1:23" s="30" customFormat="1" ht="20">
       <c r="A11" s="16"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
       <c r="L11" s="14"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="31"/>
-      <c r="Y11" s="32"/>
-      <c r="Z11" s="32"/>
-      <c r="AA11" s="33"/>
-      <c r="AB11" s="34"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="26"/>
+      <c r="T11" s="27"/>
+      <c r="U11" s="27"/>
+      <c r="V11" s="28"/>
+      <c r="W11" s="29"/>
     </row>
-    <row r="12" spans="1:28" s="35" customFormat="1" ht="17">
-      <c r="A12" s="37"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="41"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="32"/>
-      <c r="Z12" s="32"/>
-      <c r="AA12" s="33"/>
-      <c r="AB12" s="34"/>
+    <row r="12" spans="1:23" s="30" customFormat="1">
+      <c r="A12" s="32"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="26"/>
+      <c r="T12" s="27"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="29"/>
     </row>
-    <row r="13" spans="1:28" s="35" customFormat="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="42"/>
-      <c r="M13" s="42"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="41"/>
-      <c r="V13" s="41"/>
-      <c r="W13" s="43"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="32"/>
-      <c r="AA13" s="33"/>
-      <c r="AB13" s="34"/>
+    <row r="13" spans="1:23" s="30" customFormat="1">
+      <c r="A13" s="32"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="28"/>
+      <c r="W13" s="29"/>
     </row>
-    <row r="14" spans="1:28" s="35" customFormat="1">
-      <c r="A14" s="37"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="41"/>
-      <c r="V14" s="41"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="31"/>
-      <c r="Y14" s="32"/>
-      <c r="Z14" s="32"/>
-      <c r="AA14" s="33"/>
-      <c r="AB14" s="34"/>
+    <row r="14" spans="1:23" s="30" customFormat="1">
+      <c r="A14" s="32"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="34"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="33"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="27"/>
+      <c r="U14" s="27"/>
+      <c r="V14" s="28"/>
+      <c r="W14" s="29"/>
     </row>
-    <row r="15" spans="1:28" s="35" customFormat="1">
-      <c r="A15" s="37"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="42"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-      <c r="V15" s="41"/>
-      <c r="W15" s="43"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="32"/>
-      <c r="Z15" s="32"/>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="34"/>
+    <row r="15" spans="1:23" s="30" customFormat="1">
+      <c r="A15" s="32"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="33"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="29"/>
     </row>
-    <row r="16" spans="1:28" s="2" customFormat="1" ht="18">
-      <c r="A16" s="37"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="42"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="42"/>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-      <c r="V16" s="41"/>
-      <c r="W16" s="43"/>
-      <c r="Y16" s="8"/>
+    <row r="16" spans="1:23" s="2" customFormat="1" ht="18">
+      <c r="A16" s="32"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="T16" s="8"/>
     </row>
-    <row r="17" spans="1:25" s="9" customFormat="1" ht="20">
-      <c r="A17" s="37"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="41"/>
-      <c r="U17" s="41"/>
-      <c r="V17" s="41"/>
-      <c r="W17" s="43"/>
+    <row r="17" spans="1:20" s="9" customFormat="1" ht="20">
+      <c r="A17" s="32"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
     </row>
-    <row r="18" spans="1:25" s="9" customFormat="1" ht="20">
-      <c r="A18" s="37"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="41"/>
-      <c r="V18" s="41"/>
-      <c r="W18" s="43"/>
-      <c r="Y18" s="15"/>
+    <row r="18" spans="1:20" s="9" customFormat="1" ht="20">
+      <c r="A18" s="32"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="T18" s="15"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
@@ -6057,6 +5580,5 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/thaco/color/1_DATA_NoAllowance.xlsx
+++ b/thaco/color/1_DATA_NoAllowance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B0B779-B650-5B4C-B391-23075A9557E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293D5D53-C00F-844D-94E9-CACDBA7B4355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40720" yWindow="500" windowWidth="28440" windowHeight="17560" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4161,7 +4161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>MSNV</t>
   </si>
@@ -4224,6 +4224,9 @@
   </si>
   <si>
     <t>Realization part 1</t>
+  </si>
+  <si>
+    <t>TT</t>
   </si>
 </sst>
 </file>
@@ -4419,115 +4422,118 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="1991-" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -4914,666 +4920,700 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="8.5" style="32" customWidth="1"/>
-    <col min="2" max="15" width="7.1640625" style="34" customWidth="1"/>
-    <col min="16" max="17" width="10.5" style="33" customWidth="1"/>
-    <col min="18" max="18" width="12.5" style="33" customWidth="1"/>
-    <col min="19" max="19" width="19.5" style="35" customWidth="1"/>
-    <col min="20" max="20" width="12.33203125" style="35" customWidth="1"/>
-    <col min="21" max="21" width="12.5" style="35" customWidth="1"/>
-    <col min="22" max="22" width="11.6640625" style="35" customWidth="1"/>
-    <col min="23" max="16384" width="9.1640625" style="35"/>
+    <col min="1" max="2" width="8.5" style="37" customWidth="1"/>
+    <col min="3" max="16" width="7.1640625" style="38" customWidth="1"/>
+    <col min="17" max="18" width="10.5" style="11" customWidth="1"/>
+    <col min="19" max="19" width="12.5" style="11" customWidth="1"/>
+    <col min="20" max="20" width="19.5" style="42" customWidth="1"/>
+    <col min="21" max="21" width="12.33203125" style="42" customWidth="1"/>
+    <col min="22" max="22" width="12.5" style="42" customWidth="1"/>
+    <col min="23" max="23" width="11.6640625" style="42" customWidth="1"/>
+    <col min="24" max="16384" width="9.1640625" style="42"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="41" customFormat="1" ht="54" customHeight="1" outlineLevel="1">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="37" t="s">
+    <row r="1" spans="1:24" s="6" customFormat="1" ht="54" customHeight="1" outlineLevel="1">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="37" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="37" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="38" t="s">
+      <c r="N1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="38" t="s">
+      <c r="O1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="37" t="s">
+      <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="39" t="s">
+      <c r="Q1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="39" t="s">
+      <c r="R1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="40" t="s">
+      <c r="S1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:23" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A2" s="23">
+    <row r="2" spans="1:24" s="12" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8">
         <v>2405236</v>
       </c>
-      <c r="B2" s="24">
+      <c r="C2" s="9">
         <v>26</v>
       </c>
-      <c r="C2" s="24">
-        <v>0</v>
-      </c>
-      <c r="D2" s="24">
-        <v>0</v>
-      </c>
-      <c r="E2" s="24">
-        <v>0</v>
-      </c>
-      <c r="F2" s="24">
-        <v>0</v>
-      </c>
-      <c r="G2" s="24">
-        <v>0</v>
-      </c>
-      <c r="H2" s="24">
-        <v>0</v>
-      </c>
-      <c r="I2" s="24">
-        <v>0</v>
-      </c>
-      <c r="J2" s="24">
-        <v>0</v>
-      </c>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24">
-        <v>0</v>
-      </c>
-      <c r="M2" s="24">
-        <v>0</v>
-      </c>
-      <c r="N2" s="24">
-        <v>0</v>
-      </c>
-      <c r="O2" s="24">
-        <v>0</v>
-      </c>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="25"/>
-      <c r="R2" s="33"/>
+      <c r="D2" s="9">
+        <v>0</v>
+      </c>
+      <c r="E2" s="9">
+        <v>0</v>
+      </c>
+      <c r="F2" s="9">
+        <v>0</v>
+      </c>
+      <c r="G2" s="9">
+        <v>0</v>
+      </c>
+      <c r="H2" s="9">
+        <v>0</v>
+      </c>
+      <c r="I2" s="9">
+        <v>0</v>
+      </c>
+      <c r="J2" s="9">
+        <v>0</v>
+      </c>
+      <c r="K2" s="9">
+        <v>0</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9">
+        <v>0</v>
+      </c>
+      <c r="N2" s="9">
+        <v>0</v>
+      </c>
+      <c r="O2" s="9">
+        <v>0</v>
+      </c>
+      <c r="P2" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="11"/>
     </row>
-    <row r="3" spans="1:23" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A3" s="23">
+    <row r="3" spans="1:24" s="12" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8">
         <v>2106723</v>
       </c>
-      <c r="B3" s="24">
+      <c r="C3" s="9">
         <v>19</v>
       </c>
-      <c r="C3" s="24">
+      <c r="D3" s="9">
         <v>5</v>
       </c>
-      <c r="D3" s="24">
-        <v>0</v>
-      </c>
-      <c r="E3" s="24">
-        <v>0</v>
-      </c>
-      <c r="F3" s="24">
-        <v>0</v>
-      </c>
-      <c r="G3" s="24">
-        <v>0</v>
-      </c>
-      <c r="H3" s="24">
-        <v>0</v>
-      </c>
-      <c r="I3" s="24">
-        <v>0</v>
-      </c>
-      <c r="J3" s="24">
-        <v>0</v>
-      </c>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24">
-        <v>0</v>
-      </c>
-      <c r="M3" s="24">
-        <v>0</v>
-      </c>
-      <c r="N3" s="24">
-        <v>0</v>
-      </c>
-      <c r="O3" s="24">
-        <v>0</v>
-      </c>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="33"/>
+      <c r="E3" s="9">
+        <v>0</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0</v>
+      </c>
+      <c r="H3" s="9">
+        <v>0</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0</v>
+      </c>
+      <c r="J3" s="9">
+        <v>0</v>
+      </c>
+      <c r="K3" s="9">
+        <v>0</v>
+      </c>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9">
+        <v>0</v>
+      </c>
+      <c r="N3" s="9">
+        <v>0</v>
+      </c>
+      <c r="O3" s="9">
+        <v>0</v>
+      </c>
+      <c r="P3" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="11"/>
     </row>
-    <row r="4" spans="1:23" s="1" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A4" s="31" t="s">
+    <row r="4" spans="1:24" s="12" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="24">
+      <c r="C4" s="9">
         <v>24</v>
       </c>
-      <c r="C4" s="24">
-        <v>0</v>
-      </c>
-      <c r="D4" s="24">
-        <v>0</v>
-      </c>
-      <c r="E4" s="24">
-        <v>0</v>
-      </c>
-      <c r="F4" s="24">
-        <v>0</v>
-      </c>
-      <c r="G4" s="24">
-        <v>0</v>
-      </c>
-      <c r="H4" s="24">
-        <v>0</v>
-      </c>
-      <c r="I4" s="24">
-        <v>0</v>
-      </c>
-      <c r="J4" s="24">
-        <v>0</v>
-      </c>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24">
+      <c r="D4" s="9">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9">
         <v>2</v>
       </c>
-      <c r="M4" s="24">
-        <v>0</v>
-      </c>
-      <c r="N4" s="24">
-        <v>0</v>
-      </c>
-      <c r="O4" s="24">
-        <v>0</v>
-      </c>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="33"/>
+      <c r="N4" s="9">
+        <v>0</v>
+      </c>
+      <c r="O4" s="9">
+        <v>0</v>
+      </c>
+      <c r="P4" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="11"/>
     </row>
-    <row r="5" spans="1:23" s="18" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A5" s="23">
+    <row r="5" spans="1:24" s="14" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8">
         <v>2406198</v>
       </c>
-      <c r="B5" s="24">
+      <c r="C5" s="9">
         <v>23</v>
       </c>
-      <c r="C5" s="24">
+      <c r="D5" s="9">
         <v>3</v>
       </c>
-      <c r="D5" s="24">
-        <v>0</v>
-      </c>
-      <c r="E5" s="24">
-        <v>0</v>
-      </c>
-      <c r="F5" s="24">
-        <v>0</v>
-      </c>
-      <c r="G5" s="24">
-        <v>0</v>
-      </c>
-      <c r="H5" s="24">
-        <v>0</v>
-      </c>
-      <c r="I5" s="24">
-        <v>0</v>
-      </c>
-      <c r="J5" s="24">
-        <v>0</v>
-      </c>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24">
-        <v>0</v>
-      </c>
-      <c r="M5" s="24">
-        <v>0</v>
-      </c>
-      <c r="N5" s="24">
-        <v>0</v>
-      </c>
-      <c r="O5" s="24">
-        <v>0</v>
-      </c>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="33"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="20"/>
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9">
+        <v>0</v>
+      </c>
+      <c r="N5" s="9">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
+      </c>
+      <c r="P5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="11"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="16"/>
     </row>
-    <row r="6" spans="1:23" s="18" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A6" s="31" t="s">
+    <row r="6" spans="1:24" s="14" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="24">
+      <c r="C6" s="9">
         <v>22</v>
       </c>
-      <c r="C6" s="24">
-        <v>0</v>
-      </c>
-      <c r="D6" s="24">
+      <c r="D6" s="9">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9">
         <v>2</v>
       </c>
-      <c r="E6" s="24">
+      <c r="F6" s="9">
         <v>2</v>
       </c>
-      <c r="F6" s="24">
-        <v>0</v>
-      </c>
-      <c r="G6" s="24">
-        <v>0</v>
-      </c>
-      <c r="H6" s="24">
-        <v>0</v>
-      </c>
-      <c r="I6" s="24">
-        <v>0</v>
-      </c>
-      <c r="J6" s="24">
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
         <v>2</v>
       </c>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24">
-        <v>0</v>
-      </c>
-      <c r="M6" s="24">
-        <v>0</v>
-      </c>
-      <c r="N6" s="24">
-        <v>0</v>
-      </c>
-      <c r="O6" s="24">
-        <v>0</v>
-      </c>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
-      <c r="R6" s="33"/>
-      <c r="V6" s="19"/>
-      <c r="W6" s="20"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9">
+        <v>0</v>
+      </c>
+      <c r="N6" s="9">
+        <v>0</v>
+      </c>
+      <c r="O6" s="9">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="11"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="16"/>
     </row>
-    <row r="7" spans="1:23" s="21" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A7" s="23">
+    <row r="7" spans="1:24" s="17" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8">
         <v>2406145</v>
       </c>
-      <c r="B7" s="24">
+      <c r="C7" s="9">
         <v>26</v>
       </c>
-      <c r="C7" s="24">
-        <v>0</v>
-      </c>
-      <c r="D7" s="24">
-        <v>0</v>
-      </c>
-      <c r="E7" s="24">
-        <v>0</v>
-      </c>
-      <c r="F7" s="24">
-        <v>0</v>
-      </c>
-      <c r="G7" s="24">
-        <v>0</v>
-      </c>
-      <c r="H7" s="24">
-        <v>0</v>
-      </c>
-      <c r="I7" s="24">
-        <v>0</v>
-      </c>
-      <c r="J7" s="24">
-        <v>0</v>
-      </c>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24">
-        <v>0</v>
-      </c>
-      <c r="M7" s="24">
-        <v>0</v>
-      </c>
-      <c r="N7" s="24">
-        <v>0</v>
-      </c>
-      <c r="O7" s="24">
-        <v>0</v>
-      </c>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="R7" s="33"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="20"/>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <v>0</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>0</v>
+      </c>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9">
+        <v>0</v>
+      </c>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="11"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="16"/>
     </row>
-    <row r="8" spans="1:23" s="21" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A8" s="31" t="s">
+    <row r="8" spans="1:24" s="17" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="24">
+      <c r="C8" s="9">
         <v>26</v>
       </c>
-      <c r="C8" s="24">
-        <v>0</v>
-      </c>
-      <c r="D8" s="24">
-        <v>0</v>
-      </c>
-      <c r="E8" s="24">
-        <v>0</v>
-      </c>
-      <c r="F8" s="24">
-        <v>0</v>
-      </c>
-      <c r="G8" s="24">
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
         <v>5</v>
       </c>
-      <c r="H8" s="24">
+      <c r="I8" s="9">
         <v>2</v>
       </c>
-      <c r="I8" s="24">
-        <v>0</v>
-      </c>
-      <c r="J8" s="24">
-        <v>0</v>
-      </c>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24">
-        <v>0</v>
-      </c>
-      <c r="M8" s="24">
-        <v>0</v>
-      </c>
-      <c r="N8" s="24">
-        <v>0</v>
-      </c>
-      <c r="O8" s="24">
-        <v>0</v>
-      </c>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="18"/>
-      <c r="T8" s="22"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="20"/>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+      <c r="O8" s="9">
+        <v>0</v>
+      </c>
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="18"/>
+      <c r="W8" s="15"/>
+      <c r="X8" s="16"/>
     </row>
-    <row r="9" spans="1:23" s="30" customFormat="1" ht="18">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="26"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="28"/>
-      <c r="W9" s="29"/>
+    <row r="9" spans="1:24" s="28" customFormat="1" ht="18">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="27"/>
     </row>
-    <row r="10" spans="1:23" s="30" customFormat="1" ht="20">
-      <c r="A10" s="10"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
-      <c r="S10" s="26"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="28"/>
-      <c r="W10" s="29"/>
+    <row r="10" spans="1:24" s="28" customFormat="1" ht="20">
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="26"/>
+      <c r="X10" s="27"/>
     </row>
-    <row r="11" spans="1:23" s="30" customFormat="1" ht="20">
-      <c r="A11" s="16"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="26"/>
-      <c r="T11" s="27"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="28"/>
-      <c r="W11" s="29"/>
+    <row r="11" spans="1:24" s="28" customFormat="1" ht="20">
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="26"/>
+      <c r="X11" s="27"/>
     </row>
-    <row r="12" spans="1:23" s="30" customFormat="1">
-      <c r="A12" s="32"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="26"/>
-      <c r="T12" s="27"/>
-      <c r="U12" s="27"/>
-      <c r="V12" s="28"/>
-      <c r="W12" s="29"/>
+    <row r="12" spans="1:24" s="28" customFormat="1">
+      <c r="A12" s="37"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="26"/>
+      <c r="X12" s="27"/>
     </row>
-    <row r="13" spans="1:23" s="30" customFormat="1">
-      <c r="A13" s="32"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="26"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="28"/>
-      <c r="W13" s="29"/>
+    <row r="13" spans="1:24" s="28" customFormat="1">
+      <c r="A13" s="37"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="26"/>
+      <c r="X13" s="27"/>
     </row>
-    <row r="14" spans="1:23" s="30" customFormat="1">
-      <c r="A14" s="32"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="26"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="28"/>
-      <c r="W14" s="29"/>
+    <row r="14" spans="1:24" s="28" customFormat="1">
+      <c r="A14" s="37"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="38"/>
+      <c r="L14" s="38"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="38"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="26"/>
+      <c r="X14" s="27"/>
     </row>
-    <row r="15" spans="1:23" s="30" customFormat="1">
-      <c r="A15" s="32"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="26"/>
-      <c r="T15" s="27"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="28"/>
-      <c r="W15" s="29"/>
+    <row r="15" spans="1:24" s="28" customFormat="1">
+      <c r="A15" s="37"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="24"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="26"/>
+      <c r="X15" s="27"/>
     </row>
-    <row r="16" spans="1:23" s="2" customFormat="1" ht="18">
-      <c r="A16" s="32"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="T16" s="8"/>
+    <row r="16" spans="1:24" s="39" customFormat="1" ht="18">
+      <c r="A16" s="37"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="U16" s="40"/>
     </row>
-    <row r="17" spans="1:20" s="9" customFormat="1" ht="20">
-      <c r="A17" s="32"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
+    <row r="17" spans="1:21" s="31" customFormat="1" ht="20">
+      <c r="A17" s="37"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="38"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
     </row>
-    <row r="18" spans="1:20" s="9" customFormat="1" ht="20">
-      <c r="A18" s="32"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="T18" s="15"/>
+    <row r="18" spans="1:21" s="31" customFormat="1" ht="20">
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
+      <c r="S18" s="11"/>
+      <c r="U18" s="41"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1">
+  <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="5" priority="14"/>
     <cfRule type="duplicateValues" dxfId="4" priority="15"/>
     <cfRule type="duplicateValues" dxfId="3" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A1048576">
+  <conditionalFormatting sqref="A9:A1048576 B2:B1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="17"/>
     <cfRule type="duplicateValues" dxfId="1" priority="18"/>
     <cfRule type="duplicateValues" dxfId="0" priority="19"/>
